--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoV1.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoV1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haqua\source\repos\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287F7ED9-8703-4FF4-A84E-AB739DF409C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3966D29-FAFF-4A31-A697-B04684A3ADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F30A999D-8AA9-4EB0-A60C-86C78673A0AD}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{F30A999D-8AA9-4EB0-A60C-86C78673A0AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021" concurrentCalc="0"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -106,11 +106,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -156,8 +156,26 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -194,7 +212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -276,11 +294,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -298,20 +355,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -639,32 +701,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8AE389-ADB7-4203-A796-E150C4B1ABD0}">
   <dimension ref="A1:CM6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.25" customWidth="1"/>
+    <col min="1" max="6" width="9.140625" style="14"/>
+    <col min="7" max="7" width="17.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.28515625" style="14" customWidth="1"/>
+    <col min="14" max="91" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:91" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
       <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
@@ -748,14 +812,14 @@
       <c r="CM1" s="2"/>
     </row>
     <row r="2" spans="1:91" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
@@ -853,14 +917,14 @@
       <c r="CM2" s="2"/>
     </row>
     <row r="3" spans="1:91" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="6">
         <v>0</v>
       </c>
@@ -1050,217 +1114,217 @@
       <c r="CL4" s="2"/>
       <c r="CM4" s="2"/>
     </row>
-    <row r="5" spans="1:91" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:91" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
-      <c r="AN5" s="13"/>
-      <c r="AO5" s="13"/>
-      <c r="AP5" s="13"/>
-      <c r="AQ5" s="13"/>
-      <c r="AR5" s="13"/>
-      <c r="AS5" s="13"/>
-      <c r="AT5" s="13"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="13"/>
-      <c r="AW5" s="13"/>
-      <c r="AX5" s="13"/>
-      <c r="AY5" s="13"/>
-      <c r="AZ5" s="13"/>
-      <c r="BA5" s="13"/>
-      <c r="BB5" s="13"/>
-      <c r="BC5" s="13"/>
-      <c r="BD5" s="13"/>
-      <c r="BE5" s="13"/>
-      <c r="BF5" s="13"/>
-      <c r="BG5" s="13"/>
-      <c r="BH5" s="13"/>
-      <c r="BI5" s="13"/>
-      <c r="BJ5" s="13"/>
-      <c r="BK5" s="13"/>
-      <c r="BL5" s="13"/>
-      <c r="BM5" s="13"/>
-      <c r="BN5" s="13"/>
-      <c r="BO5" s="13"/>
-      <c r="BP5" s="13"/>
-      <c r="BQ5" s="13"/>
-      <c r="BR5" s="13"/>
-      <c r="BS5" s="13"/>
-      <c r="BT5" s="13"/>
-      <c r="BU5" s="13"/>
-      <c r="BV5" s="13"/>
-      <c r="BW5" s="13"/>
-      <c r="BX5" s="13"/>
-      <c r="BY5" s="13"/>
-      <c r="BZ5" s="13"/>
-      <c r="CA5" s="13"/>
-      <c r="CB5" s="13"/>
-      <c r="CC5" s="13"/>
-      <c r="CD5" s="13"/>
-      <c r="CE5" s="13"/>
-      <c r="CF5" s="13"/>
-      <c r="CG5" s="13"/>
-      <c r="CH5" s="13"/>
-      <c r="CI5" s="13"/>
-      <c r="CJ5" s="13"/>
-      <c r="CK5" s="13"/>
-      <c r="CL5" s="13"/>
-      <c r="CM5" s="13"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+      <c r="BI5" s="9"/>
+      <c r="BJ5" s="9"/>
+      <c r="BK5" s="9"/>
+      <c r="BL5" s="9"/>
+      <c r="BM5" s="9"/>
+      <c r="BN5" s="9"/>
+      <c r="BO5" s="9"/>
+      <c r="BP5" s="9"/>
+      <c r="BQ5" s="9"/>
+      <c r="BR5" s="9"/>
+      <c r="BS5" s="9"/>
+      <c r="BT5" s="9"/>
+      <c r="BU5" s="9"/>
+      <c r="BV5" s="9"/>
+      <c r="BW5" s="9"/>
+      <c r="BX5" s="9"/>
+      <c r="BY5" s="9"/>
+      <c r="BZ5" s="9"/>
+      <c r="CA5" s="9"/>
+      <c r="CB5" s="9"/>
+      <c r="CC5" s="9"/>
+      <c r="CD5" s="9"/>
+      <c r="CE5" s="9"/>
+      <c r="CF5" s="9"/>
+      <c r="CG5" s="9"/>
+      <c r="CH5" s="9"/>
+      <c r="CI5" s="9"/>
+      <c r="CJ5" s="9"/>
+      <c r="CK5" s="9"/>
+      <c r="CL5" s="9"/>
+      <c r="CM5" s="9"/>
     </row>
-    <row r="6" spans="1:91" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2"/>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2"/>
-      <c r="BW6" s="2"/>
-      <c r="BX6" s="2"/>
-      <c r="BY6" s="2"/>
-      <c r="BZ6" s="2"/>
-      <c r="CA6" s="2"/>
-      <c r="CB6" s="2"/>
-      <c r="CC6" s="2"/>
-      <c r="CD6" s="2"/>
-      <c r="CE6" s="2"/>
-      <c r="CF6" s="2"/>
-      <c r="CG6" s="2"/>
-      <c r="CH6" s="2"/>
-      <c r="CI6" s="2"/>
-      <c r="CJ6" s="2"/>
-      <c r="CK6" s="2"/>
-      <c r="CL6" s="2"/>
-      <c r="CM6" s="2"/>
+    <row r="6" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="13"/>
+      <c r="BG6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="13"/>
+      <c r="BN6" s="13"/>
+      <c r="BO6" s="13"/>
+      <c r="BP6" s="13"/>
+      <c r="BQ6" s="13"/>
+      <c r="BR6" s="13"/>
+      <c r="BS6" s="13"/>
+      <c r="BT6" s="13"/>
+      <c r="BU6" s="13"/>
+      <c r="BV6" s="13"/>
+      <c r="BW6" s="13"/>
+      <c r="BX6" s="13"/>
+      <c r="BY6" s="13"/>
+      <c r="BZ6" s="13"/>
+      <c r="CA6" s="13"/>
+      <c r="CB6" s="13"/>
+      <c r="CC6" s="13"/>
+      <c r="CD6" s="13"/>
+      <c r="CE6" s="13"/>
+      <c r="CF6" s="13"/>
+      <c r="CG6" s="13"/>
+      <c r="CH6" s="13"/>
+      <c r="CI6" s="13"/>
+      <c r="CJ6" s="13"/>
+      <c r="CK6" s="13"/>
+      <c r="CL6" s="13"/>
+      <c r="CM6" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1274,11 +1338,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1509,27 +1574,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2805DAB0-0287-4ED8-AE35-4ED06A772265}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018B28C1-B173-45F8-AB6D-10704E690C54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1554,9 +1609,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018B28C1-B173-45F8-AB6D-10704E690C54}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2805DAB0-0287-4ED8-AE35-4ED06A772265}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoV1.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoV1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haqua\source\repos\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3966D29-FAFF-4A31-A697-B04684A3ADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D9FA31-DA47-4F90-A317-23895B0AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{F30A999D-8AA9-4EB0-A60C-86C78673A0AD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F30A999D-8AA9-4EB0-A60C-86C78673A0AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,78 +106,64 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="6">
@@ -337,54 +323,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,319 +680,320 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8AE389-ADB7-4203-A796-E150C4B1ABD0}">
   <dimension ref="A1:CM6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="9.140625" style="14"/>
-    <col min="7" max="7" width="17.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.28515625" style="14" customWidth="1"/>
-    <col min="14" max="91" width="9.140625" style="14"/>
+    <col min="1" max="6" width="9.125" style="15"/>
+    <col min="7" max="7" width="17.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="15" customWidth="1"/>
+    <col min="9" max="9" width="39.625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="28.75" style="15" customWidth="1"/>
+    <col min="11" max="11" width="24.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.25" style="15" customWidth="1"/>
+    <col min="14" max="91" width="9.125" style="15"/>
+    <col min="92" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:91" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
       <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2"/>
-      <c r="BH1" s="2"/>
-      <c r="BI1" s="2"/>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-      <c r="BY1" s="2"/>
-      <c r="BZ1" s="2"/>
-      <c r="CA1" s="2"/>
-      <c r="CB1" s="2"/>
-      <c r="CC1" s="2"/>
-      <c r="CD1" s="2"/>
-      <c r="CE1" s="2"/>
-      <c r="CF1" s="2"/>
-      <c r="CG1" s="2"/>
-      <c r="CH1" s="2"/>
-      <c r="CI1" s="2"/>
-      <c r="CJ1" s="2"/>
-      <c r="CK1" s="2"/>
-      <c r="CL1" s="2"/>
-      <c r="CM1" s="2"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BL1" s="9"/>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
+      <c r="BO1" s="9"/>
+      <c r="BP1" s="9"/>
+      <c r="BQ1" s="9"/>
+      <c r="BR1" s="9"/>
+      <c r="BS1" s="9"/>
+      <c r="BT1" s="9"/>
+      <c r="BU1" s="9"/>
+      <c r="BV1" s="9"/>
+      <c r="BW1" s="9"/>
+      <c r="BX1" s="9"/>
+      <c r="BY1" s="9"/>
+      <c r="BZ1" s="9"/>
+      <c r="CA1" s="9"/>
+      <c r="CB1" s="9"/>
+      <c r="CC1" s="9"/>
+      <c r="CD1" s="9"/>
+      <c r="CE1" s="9"/>
+      <c r="CF1" s="9"/>
+      <c r="CG1" s="9"/>
+      <c r="CH1" s="9"/>
+      <c r="CI1" s="9"/>
+      <c r="CJ1" s="9"/>
+      <c r="CK1" s="9"/>
+      <c r="CL1" s="9"/>
+      <c r="CM1" s="9"/>
     </row>
-    <row r="2" spans="1:91" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="4" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2"/>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
-      <c r="BR2" s="2"/>
-      <c r="BS2" s="2"/>
-      <c r="BT2" s="2"/>
-      <c r="BU2" s="2"/>
-      <c r="BV2" s="2"/>
-      <c r="BW2" s="2"/>
-      <c r="BX2" s="2"/>
-      <c r="BY2" s="2"/>
-      <c r="BZ2" s="2"/>
-      <c r="CA2" s="2"/>
-      <c r="CB2" s="2"/>
-      <c r="CC2" s="2"/>
-      <c r="CD2" s="2"/>
-      <c r="CE2" s="2"/>
-      <c r="CF2" s="2"/>
-      <c r="CG2" s="2"/>
-      <c r="CH2" s="2"/>
-      <c r="CI2" s="2"/>
-      <c r="CJ2" s="2"/>
-      <c r="CK2" s="2"/>
-      <c r="CL2" s="2"/>
-      <c r="CM2" s="2"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="9"/>
+      <c r="AN2" s="9"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="9"/>
+      <c r="AQ2" s="9"/>
+      <c r="AR2" s="9"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="9"/>
+      <c r="AU2" s="9"/>
+      <c r="AV2" s="9"/>
+      <c r="AW2" s="9"/>
+      <c r="AX2" s="9"/>
+      <c r="AY2" s="9"/>
+      <c r="AZ2" s="9"/>
+      <c r="BA2" s="9"/>
+      <c r="BB2" s="9"/>
+      <c r="BC2" s="9"/>
+      <c r="BD2" s="9"/>
+      <c r="BE2" s="9"/>
+      <c r="BF2" s="9"/>
+      <c r="BG2" s="9"/>
+      <c r="BH2" s="9"/>
+      <c r="BI2" s="9"/>
+      <c r="BJ2" s="9"/>
+      <c r="BK2" s="9"/>
+      <c r="BL2" s="9"/>
+      <c r="BM2" s="9"/>
+      <c r="BN2" s="9"/>
+      <c r="BO2" s="9"/>
+      <c r="BP2" s="9"/>
+      <c r="BQ2" s="9"/>
+      <c r="BR2" s="9"/>
+      <c r="BS2" s="9"/>
+      <c r="BT2" s="9"/>
+      <c r="BU2" s="9"/>
+      <c r="BV2" s="9"/>
+      <c r="BW2" s="9"/>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="9"/>
+      <c r="CA2" s="9"/>
+      <c r="CB2" s="9"/>
+      <c r="CC2" s="9"/>
+      <c r="CD2" s="9"/>
+      <c r="CE2" s="9"/>
+      <c r="CF2" s="9"/>
+      <c r="CG2" s="9"/>
+      <c r="CH2" s="9"/>
+      <c r="CI2" s="9"/>
+      <c r="CJ2" s="9"/>
+      <c r="CK2" s="9"/>
+      <c r="CL2" s="9"/>
+      <c r="CM2" s="9"/>
     </row>
-    <row r="3" spans="1:91" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="6">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
-      <c r="AR3" s="2"/>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2"/>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="2"/>
-      <c r="AY3" s="2"/>
-      <c r="AZ3" s="2"/>
-      <c r="BA3" s="2"/>
-      <c r="BB3" s="2"/>
-      <c r="BC3" s="2"/>
-      <c r="BD3" s="2"/>
-      <c r="BE3" s="2"/>
-      <c r="BF3" s="2"/>
-      <c r="BG3" s="2"/>
-      <c r="BH3" s="2"/>
-      <c r="BI3" s="2"/>
-      <c r="BJ3" s="2"/>
-      <c r="BK3" s="2"/>
-      <c r="BL3" s="2"/>
-      <c r="BM3" s="2"/>
-      <c r="BN3" s="2"/>
-      <c r="BO3" s="2"/>
-      <c r="BP3" s="2"/>
-      <c r="BQ3" s="2"/>
-      <c r="BR3" s="2"/>
-      <c r="BS3" s="2"/>
-      <c r="BT3" s="2"/>
-      <c r="BU3" s="2"/>
-      <c r="BV3" s="2"/>
-      <c r="BW3" s="2"/>
-      <c r="BX3" s="2"/>
-      <c r="BY3" s="2"/>
-      <c r="BZ3" s="2"/>
-      <c r="CA3" s="2"/>
-      <c r="CB3" s="2"/>
-      <c r="CC3" s="2"/>
-      <c r="CD3" s="2"/>
-      <c r="CE3" s="2"/>
-      <c r="CF3" s="2"/>
-      <c r="CG3" s="2"/>
-      <c r="CH3" s="2"/>
-      <c r="CI3" s="2"/>
-      <c r="CJ3" s="2"/>
-      <c r="CK3" s="2"/>
-      <c r="CL3" s="2"/>
-      <c r="CM3" s="2"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
+      <c r="AV3" s="9"/>
+      <c r="AW3" s="9"/>
+      <c r="AX3" s="9"/>
+      <c r="AY3" s="9"/>
+      <c r="AZ3" s="9"/>
+      <c r="BA3" s="9"/>
+      <c r="BB3" s="9"/>
+      <c r="BC3" s="9"/>
+      <c r="BD3" s="9"/>
+      <c r="BE3" s="9"/>
+      <c r="BF3" s="9"/>
+      <c r="BG3" s="9"/>
+      <c r="BH3" s="9"/>
+      <c r="BI3" s="9"/>
+      <c r="BJ3" s="9"/>
+      <c r="BK3" s="9"/>
+      <c r="BL3" s="9"/>
+      <c r="BM3" s="9"/>
+      <c r="BN3" s="9"/>
+      <c r="BO3" s="9"/>
+      <c r="BP3" s="9"/>
+      <c r="BQ3" s="9"/>
+      <c r="BR3" s="9"/>
+      <c r="BS3" s="9"/>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="9"/>
+      <c r="BV3" s="9"/>
+      <c r="BW3" s="9"/>
+      <c r="BX3" s="9"/>
+      <c r="BY3" s="9"/>
+      <c r="BZ3" s="9"/>
+      <c r="CA3" s="9"/>
+      <c r="CB3" s="9"/>
+      <c r="CC3" s="9"/>
+      <c r="CD3" s="9"/>
+      <c r="CE3" s="9"/>
+      <c r="CF3" s="9"/>
+      <c r="CG3" s="9"/>
+      <c r="CH3" s="9"/>
+      <c r="CI3" s="9"/>
+      <c r="CJ3" s="9"/>
+      <c r="CK3" s="9"/>
+      <c r="CL3" s="9"/>
+      <c r="CM3" s="9"/>
     </row>
-    <row r="4" spans="1:91" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1022,309 +1002,220 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2"/>
-      <c r="BE4" s="2"/>
-      <c r="BF4" s="2"/>
-      <c r="BG4" s="2"/>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2"/>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2"/>
-      <c r="BW4" s="2"/>
-      <c r="BX4" s="2"/>
-      <c r="BY4" s="2"/>
-      <c r="BZ4" s="2"/>
-      <c r="CA4" s="2"/>
-      <c r="CB4" s="2"/>
-      <c r="CC4" s="2"/>
-      <c r="CD4" s="2"/>
-      <c r="CE4" s="2"/>
-      <c r="CF4" s="2"/>
-      <c r="CG4" s="2"/>
-      <c r="CH4" s="2"/>
-      <c r="CI4" s="2"/>
-      <c r="CJ4" s="2"/>
-      <c r="CK4" s="2"/>
-      <c r="CL4" s="2"/>
-      <c r="CM4" s="2"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
+      <c r="AV4" s="9"/>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="9"/>
+      <c r="AY4" s="9"/>
+      <c r="AZ4" s="9"/>
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9"/>
+      <c r="BC4" s="9"/>
+      <c r="BD4" s="9"/>
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9"/>
+      <c r="BG4" s="9"/>
+      <c r="BH4" s="9"/>
+      <c r="BI4" s="9"/>
+      <c r="BJ4" s="9"/>
+      <c r="BK4" s="9"/>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="9"/>
+      <c r="BN4" s="9"/>
+      <c r="BO4" s="9"/>
+      <c r="BP4" s="9"/>
+      <c r="BQ4" s="9"/>
+      <c r="BR4" s="9"/>
+      <c r="BS4" s="9"/>
+      <c r="BT4" s="9"/>
+      <c r="BU4" s="9"/>
+      <c r="BV4" s="9"/>
+      <c r="BW4" s="9"/>
+      <c r="BX4" s="9"/>
+      <c r="BY4" s="9"/>
+      <c r="BZ4" s="9"/>
+      <c r="CA4" s="9"/>
+      <c r="CB4" s="9"/>
+      <c r="CC4" s="9"/>
+      <c r="CD4" s="9"/>
+      <c r="CE4" s="9"/>
+      <c r="CF4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+      <c r="CJ4" s="9"/>
+      <c r="CK4" s="9"/>
+      <c r="CL4" s="9"/>
+      <c r="CM4" s="9"/>
     </row>
-    <row r="5" spans="1:91" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:91" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
-      <c r="AJ5" s="9"/>
-      <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
-      <c r="AV5" s="9"/>
-      <c r="AW5" s="9"/>
-      <c r="AX5" s="9"/>
-      <c r="AY5" s="9"/>
-      <c r="AZ5" s="9"/>
-      <c r="BA5" s="9"/>
-      <c r="BB5" s="9"/>
-      <c r="BC5" s="9"/>
-      <c r="BD5" s="9"/>
-      <c r="BE5" s="9"/>
-      <c r="BF5" s="9"/>
-      <c r="BG5" s="9"/>
-      <c r="BH5" s="9"/>
-      <c r="BI5" s="9"/>
-      <c r="BJ5" s="9"/>
-      <c r="BK5" s="9"/>
-      <c r="BL5" s="9"/>
-      <c r="BM5" s="9"/>
-      <c r="BN5" s="9"/>
-      <c r="BO5" s="9"/>
-      <c r="BP5" s="9"/>
-      <c r="BQ5" s="9"/>
-      <c r="BR5" s="9"/>
-      <c r="BS5" s="9"/>
-      <c r="BT5" s="9"/>
-      <c r="BU5" s="9"/>
-      <c r="BV5" s="9"/>
-      <c r="BW5" s="9"/>
-      <c r="BX5" s="9"/>
-      <c r="BY5" s="9"/>
-      <c r="BZ5" s="9"/>
-      <c r="CA5" s="9"/>
-      <c r="CB5" s="9"/>
-      <c r="CC5" s="9"/>
-      <c r="CD5" s="9"/>
-      <c r="CE5" s="9"/>
-      <c r="CF5" s="9"/>
-      <c r="CG5" s="9"/>
-      <c r="CH5" s="9"/>
-      <c r="CI5" s="9"/>
-      <c r="CJ5" s="9"/>
-      <c r="CK5" s="9"/>
-      <c r="CL5" s="9"/>
-      <c r="CM5" s="9"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="14"/>
+      <c r="AL5" s="14"/>
+      <c r="AM5" s="14"/>
+      <c r="AN5" s="14"/>
+      <c r="AO5" s="14"/>
+      <c r="AP5" s="14"/>
+      <c r="AQ5" s="14"/>
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="14"/>
+      <c r="AV5" s="14"/>
+      <c r="AW5" s="14"/>
+      <c r="AX5" s="14"/>
+      <c r="AY5" s="14"/>
+      <c r="AZ5" s="14"/>
+      <c r="BA5" s="14"/>
+      <c r="BB5" s="14"/>
+      <c r="BC5" s="14"/>
+      <c r="BD5" s="14"/>
+      <c r="BE5" s="14"/>
+      <c r="BF5" s="14"/>
+      <c r="BG5" s="14"/>
+      <c r="BH5" s="14"/>
+      <c r="BI5" s="14"/>
+      <c r="BJ5" s="14"/>
+      <c r="BK5" s="14"/>
+      <c r="BL5" s="14"/>
+      <c r="BM5" s="14"/>
+      <c r="BN5" s="14"/>
+      <c r="BO5" s="14"/>
+      <c r="BP5" s="14"/>
+      <c r="BQ5" s="14"/>
+      <c r="BR5" s="14"/>
+      <c r="BS5" s="14"/>
+      <c r="BT5" s="14"/>
+      <c r="BU5" s="14"/>
+      <c r="BV5" s="14"/>
+      <c r="BW5" s="14"/>
+      <c r="BX5" s="14"/>
+      <c r="BY5" s="14"/>
+      <c r="BZ5" s="14"/>
+      <c r="CA5" s="14"/>
+      <c r="CB5" s="14"/>
+      <c r="CC5" s="14"/>
+      <c r="CD5" s="14"/>
+      <c r="CE5" s="14"/>
+      <c r="CF5" s="14"/>
+      <c r="CG5" s="14"/>
+      <c r="CH5" s="14"/>
+      <c r="CI5" s="14"/>
+      <c r="CJ5" s="14"/>
+      <c r="CK5" s="14"/>
+      <c r="CL5" s="14"/>
+      <c r="CM5" s="14"/>
     </row>
     <row r="6" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="13"/>
-      <c r="BP6" s="13"/>
-      <c r="BQ6" s="13"/>
-      <c r="BR6" s="13"/>
-      <c r="BS6" s="13"/>
-      <c r="BT6" s="13"/>
-      <c r="BU6" s="13"/>
-      <c r="BV6" s="13"/>
-      <c r="BW6" s="13"/>
-      <c r="BX6" s="13"/>
-      <c r="BY6" s="13"/>
-      <c r="BZ6" s="13"/>
-      <c r="CA6" s="13"/>
-      <c r="CB6" s="13"/>
-      <c r="CC6" s="13"/>
-      <c r="CD6" s="13"/>
-      <c r="CE6" s="13"/>
-      <c r="CF6" s="13"/>
-      <c r="CG6" s="13"/>
-      <c r="CH6" s="13"/>
-      <c r="CI6" s="13"/>
-      <c r="CJ6" s="13"/>
-      <c r="CK6" s="13"/>
-      <c r="CL6" s="13"/>
-      <c r="CM6" s="13"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1338,12 +1229,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1574,17 +1464,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018B28C1-B173-45F8-AB6D-10704E690C54}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2805DAB0-0287-4ED8-AE35-4ED06A772265}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1609,18 +1509,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2805DAB0-0287-4ED8-AE35-4ED06A772265}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018B28C1-B173-45F8-AB6D-10704E690C54}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>